--- a/data/calibrations/Base de données BCIAT BCIB France 2030_17.05.24_hg (1).xlsx
+++ b/data/calibrations/Base de données BCIAT BCIB France 2030_17.05.24_hg (1).xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\callonnecg\Documents\Github\ThreeME\data\calibrations\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\ThreeME\data\calibrations\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83EF0E63-07C2-404B-8CCE-9D1B97213A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A0B8DE7-C874-4D1A-87E7-410D3C7CC75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{81135BED-B115-4297-ADDF-3393BE6F8757}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{81135BED-B115-4297-ADDF-3393BE6F8757}"/>
   </bookViews>
   <sheets>
     <sheet name="3ME BCIAT (FDI + FC)" sheetId="7" r:id="rId1"/>
     <sheet name="BCIAT BCIB France 2030-FDI + FC" sheetId="2" r:id="rId2"/>
     <sheet name="BCIAT BCIB France 2030-FDI" sheetId="1" r:id="rId3"/>
     <sheet name="3ME-NAF" sheetId="4" r:id="rId4"/>
+    <sheet name="BCIATBCIBFrance 2030_2024" sheetId="8" r:id="rId5"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId5"/>
+    <externalReference r:id="rId6"/>
+    <externalReference r:id="rId7"/>
   </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'BCIAT BCIB France 2030-FDI + FC'!$A$1:$BT$293</definedName>
@@ -66,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15507" uniqueCount="2884">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15512" uniqueCount="2889">
   <si>
     <t>Secteur 3ME</t>
   </si>
@@ -8721,6 +8723,21 @@
   </si>
   <si>
     <t>Activités des organisations et organismes extraterritoriaux</t>
+  </si>
+  <si>
+    <t>Prod MWh</t>
+  </si>
+  <si>
+    <t>Subv €</t>
+  </si>
+  <si>
+    <t>Coût total</t>
+  </si>
+  <si>
+    <t>secteurs 3ME</t>
+  </si>
+  <si>
+    <t>total</t>
   </si>
 </sst>
 </file>
@@ -8899,7 +8916,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -8946,6 +8963,10 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="11" borderId="3" xfId="2" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="9" fontId="1" fillId="11" borderId="3" xfId="4" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8980,6 +9001,38 @@
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
+<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Synthèse FC+F2030BCIAT BCIB"/>
+      <sheetName val="Synthèse FC uniquement"/>
+      <sheetName val="bilan RC"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="44">
+          <cell r="C44">
+            <v>2035580</v>
+          </cell>
+          <cell r="G44">
+            <v>209041027</v>
+          </cell>
+          <cell r="O44">
+            <v>539871482</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
     </sheetDataSet>
@@ -90517,4 +90570,520 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{896FAF81-FB21-4E4E-B98B-BA0AB8A6E43C}">
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="44" t="s">
+        <v>2884</v>
+      </c>
+      <c r="C1" s="44"/>
+      <c r="D1" s="44" t="s">
+        <v>2885</v>
+      </c>
+      <c r="E1" s="44"/>
+      <c r="F1" s="44" t="s">
+        <v>2886</v>
+      </c>
+      <c r="G1" s="44"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2887</v>
+      </c>
+      <c r="B2">
+        <v>2023</v>
+      </c>
+      <c r="C2">
+        <v>2024</v>
+      </c>
+      <c r="D2">
+        <v>2023</v>
+      </c>
+      <c r="E2">
+        <v>2024</v>
+      </c>
+      <c r="F2">
+        <v>2023</v>
+      </c>
+      <c r="G2">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <f>'3ME BCIAT (FDI + FC)'!Q35</f>
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C17" si="0">(B3*$C$18)/$B$18</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>'3ME BCIAT (FDI + FC)'!Q18</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E17" si="1">(D3*$E$18)/$D$18</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>'3ME BCIAT (FDI + FC)'!Q2</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f t="shared" ref="G3:G17" si="2">F3/$G$18*$F$18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <f>'3ME BCIAT (FDI + FC)'!Q36</f>
+        <v>353645</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>268449.74518867896</v>
+      </c>
+      <c r="D4">
+        <f>'3ME BCIAT (FDI + FC)'!Q19</f>
+        <v>17872498</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>15503187.867811639</v>
+      </c>
+      <c r="F4">
+        <f>'3ME BCIAT (FDI + FC)'!Q3</f>
+        <v>106050826</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="2"/>
+        <v>141878181.79634354</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <f>'3ME BCIAT (FDI + FC)'!Q37</f>
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>'3ME BCIAT (FDI + FC)'!Q20</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>'3ME BCIAT (FDI + FC)'!Q4</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <f>'3ME BCIAT (FDI + FC)'!Q38</f>
+        <v>0</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f>'3ME BCIAT (FDI + FC)'!Q21</f>
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <f>'3ME BCIAT (FDI + FC)'!Q5</f>
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>5</v>
+      </c>
+      <c r="B7">
+        <f>'3ME BCIAT (FDI + FC)'!Q39</f>
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <f>'3ME BCIAT (FDI + FC)'!Q22</f>
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <f>'3ME BCIAT (FDI + FC)'!Q6</f>
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>6</v>
+      </c>
+      <c r="B8">
+        <f>'3ME BCIAT (FDI + FC)'!Q40</f>
+        <v>44000</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>33400.129475326597</v>
+      </c>
+      <c r="D8">
+        <f>'3ME BCIAT (FDI + FC)'!Q23</f>
+        <v>4600000</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>3990190.0781823299</v>
+      </c>
+      <c r="F8">
+        <f>'3ME BCIAT (FDI + FC)'!Q7</f>
+        <v>10900000</v>
+      </c>
+      <c r="G8">
+        <f t="shared" si="2"/>
+        <v>14582368.095653918</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>7</v>
+      </c>
+      <c r="B9">
+        <f>'3ME BCIAT (FDI + FC)'!Q41</f>
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <f>'3ME BCIAT (FDI + FC)'!Q24</f>
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <f>'3ME BCIAT (FDI + FC)'!Q8</f>
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>8</v>
+      </c>
+      <c r="B10">
+        <f>'3ME BCIAT (FDI + FC)'!Q42</f>
+        <v>0</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <f>'3ME BCIAT (FDI + FC)'!Q25</f>
+        <v>0</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <f>'3ME BCIAT (FDI + FC)'!Q9</f>
+        <v>0</v>
+      </c>
+      <c r="G10">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <f>'3ME BCIAT (FDI + FC)'!Q43</f>
+        <v>43311</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>32877.113811497053</v>
+      </c>
+      <c r="D11">
+        <f>'3ME BCIAT (FDI + FC)'!Q26</f>
+        <v>4500000</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>3903446.8156131487</v>
+      </c>
+      <c r="F11">
+        <f>'3ME BCIAT (FDI + FC)'!Q10</f>
+        <v>9288600</v>
+      </c>
+      <c r="G11">
+        <f t="shared" si="2"/>
+        <v>12426585.714980824</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <f>'3ME BCIAT (FDI + FC)'!Q44</f>
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f>'3ME BCIAT (FDI + FC)'!Q27</f>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F12">
+        <f>'3ME BCIAT (FDI + FC)'!Q11</f>
+        <v>0</v>
+      </c>
+      <c r="G12">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>11</v>
+      </c>
+      <c r="B13">
+        <f>'3ME BCIAT (FDI + FC)'!Q45</f>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D13">
+        <f>'3ME BCIAT (FDI + FC)'!Q28</f>
+        <v>0</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f>'3ME BCIAT (FDI + FC)'!Q12</f>
+        <v>0</v>
+      </c>
+      <c r="G13">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>12</v>
+      </c>
+      <c r="B14">
+        <f>'3ME BCIAT (FDI + FC)'!Q46</f>
+        <v>675684</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>512907.57010014949</v>
+      </c>
+      <c r="D14">
+        <f>'3ME BCIAT (FDI + FC)'!Q29</f>
+        <v>83890691.900000006</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>72769523.14591974</v>
+      </c>
+      <c r="F14">
+        <f>'3ME BCIAT (FDI + FC)'!Q13</f>
+        <v>227752981.62111899</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="2"/>
+        <v>304695212.19099617</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>18</v>
+      </c>
+      <c r="B15">
+        <f>'3ME BCIAT (FDI + FC)'!Q47</f>
+        <v>0</v>
+      </c>
+      <c r="C15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="D15">
+        <f>'3ME BCIAT (FDI + FC)'!Q30</f>
+        <v>0</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f>'3ME BCIAT (FDI + FC)'!Q14</f>
+        <v>0</v>
+      </c>
+      <c r="G15">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>19</v>
+      </c>
+      <c r="B16">
+        <f>'3ME BCIAT (FDI + FC)'!Q48</f>
+        <v>64651</v>
+      </c>
+      <c r="C16">
+        <f t="shared" si="0"/>
+        <v>49076.176607030451</v>
+      </c>
+      <c r="D16">
+        <f>'3ME BCIAT (FDI + FC)'!Q31</f>
+        <v>9639492</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>8361609.8558952054</v>
+      </c>
+      <c r="F16">
+        <f>'3ME BCIAT (FDI + FC)'!Q15</f>
+        <v>37010940</v>
+      </c>
+      <c r="G16">
+        <f t="shared" si="2"/>
+        <v>49514417.490473516</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>2402</v>
+      </c>
+      <c r="B17">
+        <f>'3ME BCIAT (FDI + FC)'!Q49</f>
+        <v>1500301</v>
+      </c>
+      <c r="C17">
+        <f t="shared" si="0"/>
+        <v>1138869.2648173175</v>
+      </c>
+      <c r="D17">
+        <f>'3ME BCIAT (FDI + FC)'!Q32</f>
+        <v>120485518</v>
+      </c>
+      <c r="E17">
+        <f t="shared" si="1"/>
+        <v>104513069.23657793</v>
+      </c>
+      <c r="F17">
+        <f>'3ME BCIAT (FDI + FC)'!Q16</f>
+        <v>331253962</v>
+      </c>
+      <c r="G17">
+        <f t="shared" si="2"/>
+        <v>443162129.08511513</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>2888</v>
+      </c>
+      <c r="B18" s="45">
+        <f>'3ME BCIAT (FDI + FC)'!Q50</f>
+        <v>2681592</v>
+      </c>
+      <c r="C18">
+        <f>'[2]Synthèse FC+F2030BCIAT BCIB'!$C$44</f>
+        <v>2035580</v>
+      </c>
+      <c r="D18">
+        <f>'3ME BCIAT (FDI + FC)'!Q33</f>
+        <v>240988199.90000001</v>
+      </c>
+      <c r="E18">
+        <f>'[2]Synthèse FC+F2030BCIAT BCIB'!$G$44</f>
+        <v>209041027</v>
+      </c>
+      <c r="F18">
+        <f>'3ME BCIAT (FDI + FC)'!Q17</f>
+        <v>722257309.62111902</v>
+      </c>
+      <c r="G18">
+        <f>'[2]Synthèse FC+F2030BCIAT BCIB'!$O$44</f>
+        <v>539871482</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>